--- a/Dataset/1_label/DOWN_DOWN_V1_5 divisions_per_second.xlsx
+++ b/Dataset/1_label/DOWN_DOWN_V1_5 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D324"/>
+  <dimension ref="A1:D327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6264,6 +6264,60 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>DOWN_DOWN_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>66200</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>DOWN_DOWN_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>66400</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>DOWN_DOWN_V1_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>66600</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
